--- a/ig/DM-MAI-2026/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/DM-MAI-2026/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,6 +438,9 @@
   </si>
   <si>
     <t>96874-3</t>
+  </si>
+  <si>
+    <t>96163-1</t>
   </si>
   <si>
     <t>96173-0</t>
@@ -854,7 +857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2161,7 +2164,7 @@
         <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -2174,7 +2177,7 @@
         <v>34</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E101" s="2"/>
     </row>
@@ -2200,9 +2203,22 @@
         <v>34</v>
       </c>
       <c r="D103" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="E103" s="2"/>
+      <c r="E104" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2233,7 +2249,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2250,7 +2266,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2263,7 +2279,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2276,7 +2292,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2289,7 +2305,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2302,7 +2318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2315,7 +2331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2328,7 +2344,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2341,7 +2357,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2354,7 +2370,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2367,7 +2383,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2380,7 +2396,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2393,7 +2409,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2406,7 +2422,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2419,7 +2435,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2432,7 +2448,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2445,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2458,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2471,7 +2487,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2484,7 +2500,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2497,7 +2513,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2510,7 +2526,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2523,7 +2539,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2536,7 +2552,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -2549,7 +2565,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -2562,7 +2578,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2575,7 +2591,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2588,20 +2604,20 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2614,7 +2630,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2627,7 +2643,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2640,7 +2656,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2653,7 +2669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2666,7 +2682,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2679,7 +2695,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2692,7 +2708,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2705,7 +2721,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -2718,20 +2734,20 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -2771,7 +2787,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2780,7 +2796,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2788,14 +2804,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2"/>
     </row>
